--- a/2024/results/v4/v1/results-sen-2-pc.xlsx
+++ b/2024/results/v4/v1/results-sen-2-pc.xlsx
@@ -1,17 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22228"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sahbab01/work/cca_fixtures/2024/results/v4/v1/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE51EBD-FB8C-F544-B67E-FC379CB22393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Fixtures" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -20,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54" count="54">
   <si>
     <t>Division ID</t>
   </si>
@@ -1021,16 +1012,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="2C7EE24B-C535-494D-AA97-0A61EE84BA40">
   <dimension ref="A1:L91"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="27.5" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="25.1640625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" x14ac:dyDescent="0.25" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1068,7 +1054,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1088,7 +1074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1108,7 +1094,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1128,7 +1114,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1148,7 +1134,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1168,7 +1154,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1188,7 +1174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1208,7 +1194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1228,7 +1214,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1248,7 +1234,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1268,7 +1254,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1288,7 +1274,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1308,7 +1294,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1328,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1348,7 +1334,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1368,7 +1354,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1388,7 +1374,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1408,7 +1394,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1428,7 +1414,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1448,7 +1434,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1468,7 +1454,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1488,7 +1474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1508,7 +1494,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1528,7 +1514,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1548,7 +1534,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1568,7 +1554,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1588,7 +1574,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1608,7 +1594,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1628,7 +1614,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1648,7 +1634,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1668,7 +1654,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1688,7 +1674,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1708,7 +1694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1728,7 +1714,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -1748,7 +1734,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1768,7 +1754,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -1788,7 +1774,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -1808,7 +1794,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -1828,7 +1814,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -1848,7 +1834,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -1868,7 +1854,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -1888,7 +1874,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -1908,7 +1894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -1928,7 +1914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -1948,7 +1934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -1968,7 +1954,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -1988,7 +1974,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -2008,7 +1994,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -2028,7 +2014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A50" t="s">
         <v>12</v>
       </c>
@@ -2048,7 +2034,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A51" t="s">
         <v>12</v>
       </c>
@@ -2068,7 +2054,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A52" t="s">
         <v>12</v>
       </c>
@@ -2088,7 +2074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A53" t="s">
         <v>12</v>
       </c>
@@ -2108,7 +2094,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A54" t="s">
         <v>12</v>
       </c>
@@ -2128,7 +2114,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A55" t="s">
         <v>12</v>
       </c>
@@ -2148,7 +2134,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -2168,7 +2154,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A57" t="s">
         <v>12</v>
       </c>
@@ -2188,7 +2174,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -2208,7 +2194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -2228,7 +2214,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2248,7 +2234,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A61" t="s">
         <v>12</v>
       </c>
@@ -2268,7 +2254,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A62" t="s">
         <v>12</v>
       </c>
@@ -2288,7 +2274,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -2308,7 +2294,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -2328,7 +2314,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -2348,7 +2334,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -2368,7 +2354,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A67" t="s">
         <v>12</v>
       </c>
@@ -2388,7 +2374,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -2408,7 +2394,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -2428,7 +2414,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -2448,7 +2434,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -2468,7 +2454,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -2488,7 +2474,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A73" t="s">
         <v>12</v>
       </c>
@@ -2508,7 +2494,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -2528,7 +2514,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A75" t="s">
         <v>12</v>
       </c>
@@ -2548,7 +2534,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -2568,7 +2554,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -2588,7 +2574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -2608,7 +2594,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -2628,7 +2614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -2648,7 +2634,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -2668,7 +2654,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -2688,7 +2674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2708,7 +2694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -2728,7 +2714,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -2748,7 +2734,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A86" t="s">
         <v>12</v>
       </c>
@@ -2768,7 +2754,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A87" t="s">
         <v>12</v>
       </c>
@@ -2788,7 +2774,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A88" t="s">
         <v>12</v>
       </c>
@@ -2808,7 +2794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A89" t="s">
         <v>12</v>
       </c>
@@ -2828,7 +2814,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -2848,7 +2834,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" x14ac:dyDescent="0.25" spans="1:6">
       <c r="A91" t="s">
         <v>12</v>
       </c>
